--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/CodeSystem-jp-observation-dental-category-cs.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/CodeSystem-jp-observation-dental-category-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t>Level</t>
@@ -160,6 +160,12 @@
   </si>
   <si>
     <t>MissingToothCondition</t>
+  </si>
+  <si>
+    <t>DO-1-04</t>
+  </si>
+  <si>
+    <t>ClinicalInformationSharing</t>
   </si>
 </sst>
 </file>
@@ -471,7 +477,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -524,6 +530,18 @@
       </c>
       <c r="D4" s="2"/>
     </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/CodeSystem-jp-observation-dental-category-cs.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/CodeSystem-jp-observation-dental-category-cs.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright Japan Dental Association 日本歯科医師会 &amp; FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan Dental Association 日本歯科医師会 &amp; FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>Case Sensitive</t>
